--- a/table.xlsx
+++ b/table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KIRIL\OneDrive\Рабочий стол\Учеба 4 сем\Алгоритмы\Сжатие\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3799E01E-A824-4C02-A243-3A0BD6716CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1B1829-8E5F-4B16-9984-279EF1D04F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
     <t>exe_file.exe</t>
   </si>
   <si>
-    <t>img.CR2</t>
+    <t>img.raw</t>
   </si>
   <si>
     <t>grey_img.raw</t>
@@ -452,12 +452,12 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -488,19 +488,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>119294</v>
+        <v>10000000</v>
       </c>
       <c r="D2">
-        <v>16393</v>
+        <v>6412991</v>
       </c>
       <c r="E2">
-        <v>119294</v>
+        <v>10000000</v>
       </c>
       <c r="F2">
-        <v>7.2771304825230283</v>
+        <v>1.559334794014213</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -508,22 +508,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>119294</v>
+        <v>2609729</v>
       </c>
       <c r="D3">
-        <v>11539</v>
+        <v>1360134</v>
       </c>
       <c r="E3">
-        <v>119294</v>
+        <v>2609729</v>
       </c>
       <c r="F3">
-        <v>10.338330877892361</v>
+        <v>1.9187293310806139</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -531,22 +531,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>119294</v>
+        <v>2874512</v>
       </c>
       <c r="D4">
-        <v>4995</v>
+        <v>2258037</v>
       </c>
       <c r="E4">
-        <v>119294</v>
+        <v>2874512</v>
       </c>
       <c r="F4">
-        <v>23.882682682682681</v>
+        <v>1.2730136840096069</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -554,22 +554,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>119294</v>
+        <v>2166048</v>
       </c>
       <c r="D5">
-        <v>16290</v>
+        <v>1926482</v>
       </c>
       <c r="E5">
-        <v>119294</v>
+        <v>2166048</v>
       </c>
       <c r="F5">
-        <v>7.323143032535298</v>
+        <v>1.1243541335968881</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -577,22 +577,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>119294</v>
+        <v>722016</v>
       </c>
       <c r="D6">
-        <v>3231</v>
+        <v>634576</v>
       </c>
       <c r="E6">
-        <v>119294</v>
+        <v>722016</v>
       </c>
       <c r="F6">
-        <v>36.921696069328377</v>
+        <v>1.1377927939285439</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -600,22 +600,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7">
-        <v>119294</v>
+        <v>948024</v>
       </c>
       <c r="D7">
-        <v>5451</v>
+        <v>118514</v>
       </c>
       <c r="E7">
-        <v>119294</v>
+        <v>948024</v>
       </c>
       <c r="F7">
-        <v>21.88479178132453</v>
+        <v>7.9992574716911076</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -623,22 +623,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>119294</v>
+        <v>10000000</v>
       </c>
       <c r="D8">
-        <v>4887</v>
+        <v>11317947</v>
       </c>
       <c r="E8">
-        <v>119294</v>
+        <v>10000000</v>
       </c>
       <c r="F8">
-        <v>24.410476775117662</v>
+        <v>0.88355246759858475</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -646,22 +646,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>119294</v>
+        <v>2609729</v>
       </c>
       <c r="D9">
-        <v>6561</v>
+        <v>2614444</v>
       </c>
       <c r="E9">
-        <v>119294</v>
+        <v>2609729</v>
       </c>
       <c r="F9">
-        <v>18.18228928516994</v>
+        <v>0.99819655727948275</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -669,22 +669,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>119294</v>
+        <v>2874512</v>
       </c>
       <c r="D10">
-        <v>5529</v>
+        <v>2985073</v>
       </c>
       <c r="E10">
-        <v>119294</v>
+        <v>2874512</v>
       </c>
       <c r="F10">
-        <v>21.576053535901611</v>
+        <v>0.96296204481431447</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -692,22 +692,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>10000000</v>
+        <v>2166048</v>
       </c>
       <c r="D11">
-        <v>6412991</v>
+        <v>2087174</v>
       </c>
       <c r="E11">
-        <v>10000000</v>
+        <v>2166048</v>
       </c>
       <c r="F11">
-        <v>1.559334794014213</v>
+        <v>1.0377898536490009</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -718,19 +718,19 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>10000000</v>
+        <v>722016</v>
       </c>
       <c r="D12">
-        <v>11317947</v>
+        <v>720072</v>
       </c>
       <c r="E12">
-        <v>10000000</v>
+        <v>722016</v>
       </c>
       <c r="F12">
-        <v>0.88355246759858475</v>
+        <v>1.0026997300269971</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -738,22 +738,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C13">
-        <v>10000000</v>
+        <v>948024</v>
       </c>
       <c r="D13">
-        <v>10845427</v>
+        <v>7275</v>
       </c>
       <c r="E13">
-        <v>10000000</v>
+        <v>948024</v>
       </c>
       <c r="F13">
-        <v>0.92204760587111967</v>
+        <v>130.3125773195876</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -761,7 +761,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -770,13 +770,13 @@
         <v>10000000</v>
       </c>
       <c r="D14">
-        <v>4622712</v>
+        <v>10845427</v>
       </c>
       <c r="E14">
         <v>10000000</v>
       </c>
       <c r="F14">
-        <v>2.1632323190369638</v>
+        <v>0.92204760587111967</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -784,22 +784,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>10000000</v>
+        <v>2609729</v>
       </c>
       <c r="D15">
-        <v>5694644</v>
+        <v>1861627</v>
       </c>
       <c r="E15">
-        <v>10000000</v>
+        <v>2609729</v>
       </c>
       <c r="F15">
-        <v>1.756036022620554</v>
+        <v>1.401853862239858</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>10000000</v>
+        <v>2874512</v>
       </c>
       <c r="D16">
-        <v>10785412</v>
+        <v>2319643</v>
       </c>
       <c r="E16">
-        <v>10000000</v>
+        <v>2874512</v>
       </c>
       <c r="F16">
-        <v>0.92717830343430552</v>
+        <v>1.2392044810343661</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -830,22 +830,22 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>10000000</v>
+        <v>2166048</v>
       </c>
       <c r="D17">
-        <v>7006504</v>
+        <v>2115998</v>
       </c>
       <c r="E17">
-        <v>10000000</v>
+        <v>2166048</v>
       </c>
       <c r="F17">
-        <v>1.427245313782737</v>
+        <v>1.0236531414490939</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -853,22 +853,22 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C18">
-        <v>10000000</v>
+        <v>722016</v>
       </c>
       <c r="D18">
-        <v>5543343</v>
+        <v>754860</v>
       </c>
       <c r="E18">
-        <v>10000000</v>
+        <v>722016</v>
       </c>
       <c r="F18">
-        <v>1.803965585387735</v>
+        <v>0.9564899451553931</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -876,22 +876,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C19">
-        <v>10000000</v>
+        <v>948024</v>
       </c>
       <c r="D19">
-        <v>5309444</v>
+        <v>9396</v>
       </c>
       <c r="E19">
-        <v>10000000</v>
+        <v>948024</v>
       </c>
       <c r="F19">
-        <v>1.883436382415937</v>
+        <v>100.89655172413789</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -899,22 +899,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C20">
-        <v>2874512</v>
+        <v>10000000</v>
       </c>
       <c r="D20">
-        <v>2258037</v>
+        <v>4622712</v>
       </c>
       <c r="E20">
-        <v>2874512</v>
+        <v>10000000</v>
       </c>
       <c r="F20">
-        <v>1.2730136840096069</v>
+        <v>2.1632323190369638</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -922,22 +922,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21">
-        <v>2874512</v>
+        <v>2609729</v>
       </c>
       <c r="D21">
-        <v>2985073</v>
+        <v>926025</v>
       </c>
       <c r="E21">
-        <v>2874512</v>
+        <v>2609729</v>
       </c>
       <c r="F21">
-        <v>0.96296204481431447</v>
+        <v>2.8182057719823979</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
@@ -954,13 +954,13 @@
         <v>2874512</v>
       </c>
       <c r="D22">
-        <v>2319643</v>
+        <v>1319092</v>
       </c>
       <c r="E22">
         <v>2874512</v>
       </c>
       <c r="F22">
-        <v>1.2392044810343661</v>
+        <v>2.1791596037274119</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -971,19 +971,19 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23">
-        <v>2874512</v>
+        <v>2166048</v>
       </c>
       <c r="D23">
-        <v>1319092</v>
+        <v>1142716</v>
       </c>
       <c r="E23">
-        <v>2874512</v>
+        <v>2166048</v>
       </c>
       <c r="F23">
-        <v>2.1791596037274119</v>
+        <v>1.8955260974730379</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -991,22 +991,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C24">
-        <v>2874512</v>
+        <v>722016</v>
       </c>
       <c r="D24">
-        <v>1517923</v>
+        <v>368798</v>
       </c>
       <c r="E24">
-        <v>2874512</v>
+        <v>722016</v>
       </c>
       <c r="F24">
-        <v>1.8937139762688879</v>
+        <v>1.9577546515978941</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1014,22 +1014,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C25">
-        <v>2874512</v>
+        <v>948024</v>
       </c>
       <c r="D25">
-        <v>2767679</v>
+        <v>119862</v>
       </c>
       <c r="E25">
-        <v>2874512</v>
+        <v>948024</v>
       </c>
       <c r="F25">
-        <v>1.0386002133917991</v>
+        <v>7.9092956900435496</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1037,22 +1037,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C26">
-        <v>2874512</v>
+        <v>10000000</v>
       </c>
       <c r="D26">
-        <v>1651474</v>
+        <v>5694644</v>
       </c>
       <c r="E26">
-        <v>2874512</v>
+        <v>10000000</v>
       </c>
       <c r="F26">
-        <v>1.7405735724570901</v>
+        <v>1.756036022620554</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1060,22 +1060,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27">
-        <v>2874512</v>
+        <v>2609729</v>
       </c>
       <c r="D27">
-        <v>2291616</v>
+        <v>961811</v>
       </c>
       <c r="E27">
-        <v>2874512</v>
+        <v>2609729</v>
       </c>
       <c r="F27">
-        <v>1.2543602418555291</v>
+        <v>2.713349088334402</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -1092,13 +1092,13 @@
         <v>2874512</v>
       </c>
       <c r="D28">
-        <v>2112903</v>
+        <v>1517923</v>
       </c>
       <c r="E28">
         <v>2874512</v>
       </c>
       <c r="F28">
-        <v>1.3604562064609691</v>
+        <v>1.8937139762688879</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1106,22 +1106,22 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29">
-        <v>472279</v>
+        <v>2166048</v>
       </c>
       <c r="D29">
-        <v>472162</v>
+        <v>1326347</v>
       </c>
       <c r="E29">
-        <v>472279</v>
+        <v>2166048</v>
       </c>
       <c r="F29">
-        <v>1.0002477963072001</v>
+        <v>1.6330929990417291</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1129,22 +1129,22 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
       </c>
       <c r="C30">
-        <v>472279</v>
+        <v>722016</v>
       </c>
       <c r="D30">
-        <v>477904</v>
+        <v>426709</v>
       </c>
       <c r="E30">
-        <v>472279</v>
+        <v>722016</v>
       </c>
       <c r="F30">
-        <v>0.98822985369446581</v>
+        <v>1.6920571162080009</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1152,22 +1152,22 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31">
-        <v>472279</v>
+        <v>948024</v>
       </c>
       <c r="D31">
-        <v>485024</v>
+        <v>5484</v>
       </c>
       <c r="E31">
-        <v>472279</v>
+        <v>948024</v>
       </c>
       <c r="F31">
-        <v>0.97372294979217522</v>
+        <v>172.87089715536109</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1175,22 +1175,22 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C32">
-        <v>472279</v>
+        <v>10000000</v>
       </c>
       <c r="D32">
-        <v>472994</v>
+        <v>9376509</v>
       </c>
       <c r="E32">
-        <v>472279</v>
+        <v>10000000</v>
       </c>
       <c r="F32">
-        <v>0.99848835291779603</v>
+        <v>1.066495003630882</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1198,22 +1198,22 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C33">
-        <v>472279</v>
+        <v>2609729</v>
       </c>
       <c r="D33">
-        <v>479093</v>
+        <v>1805100</v>
       </c>
       <c r="E33">
-        <v>472279</v>
+        <v>2609729</v>
       </c>
       <c r="F33">
-        <v>0.98577729167405914</v>
+        <v>1.4457531438701461</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
@@ -1224,19 +1224,19 @@
         <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>472279</v>
+        <v>2874512</v>
       </c>
       <c r="D34">
-        <v>1856200</v>
+        <v>2322664</v>
       </c>
       <c r="E34">
-        <v>472279</v>
+        <v>2874512</v>
       </c>
       <c r="F34">
-        <v>0.25443325072729228</v>
+        <v>1.2375926952843801</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
@@ -1244,22 +1244,22 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C35">
-        <v>472279</v>
+        <v>2166048</v>
       </c>
       <c r="D35">
-        <v>697005</v>
+        <v>2399774</v>
       </c>
       <c r="E35">
-        <v>472279</v>
+        <v>2166048</v>
       </c>
       <c r="F35">
-        <v>0.67758337458124407</v>
+        <v>0.9026049953037244</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
@@ -1267,22 +1267,22 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
       </c>
       <c r="C36">
-        <v>472279</v>
+        <v>722016</v>
       </c>
       <c r="D36">
-        <v>551385</v>
+        <v>804194</v>
       </c>
       <c r="E36">
-        <v>472279</v>
+        <v>722016</v>
       </c>
       <c r="F36">
-        <v>0.85653218712877577</v>
+        <v>0.89781321422442839</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
@@ -1290,22 +1290,22 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C37">
-        <v>472279</v>
+        <v>948024</v>
       </c>
       <c r="D37">
-        <v>525233</v>
+        <v>4924</v>
       </c>
       <c r="E37">
-        <v>472279</v>
+        <v>948024</v>
       </c>
       <c r="F37">
-        <v>0.89917998297898261</v>
+        <v>192.53127538586509</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
@@ -1313,22 +1313,22 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C38">
-        <v>22401100</v>
+        <v>10000000</v>
       </c>
       <c r="D38">
-        <v>22194912</v>
+        <v>6426746</v>
       </c>
       <c r="E38">
-        <v>22401100</v>
+        <v>10000000</v>
       </c>
       <c r="F38">
-        <v>1.009289876887099</v>
+        <v>1.5559973896587791</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
@@ -1336,22 +1336,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C39">
-        <v>22401100</v>
+        <v>2609729</v>
       </c>
       <c r="D39">
-        <v>22775513</v>
+        <v>1274467</v>
       </c>
       <c r="E39">
-        <v>22401100</v>
+        <v>2609729</v>
       </c>
       <c r="F39">
-        <v>0.9835607215521337</v>
+        <v>2.047702294370902</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
@@ -1359,22 +1359,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C40">
-        <v>22401100</v>
+        <v>2874512</v>
       </c>
       <c r="D40">
-        <v>22810087</v>
+        <v>1575586</v>
       </c>
       <c r="E40">
-        <v>22401100</v>
+        <v>2874512</v>
       </c>
       <c r="F40">
-        <v>0.98206990617791157</v>
+        <v>1.8244081884454419</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
@@ -1382,22 +1382,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
       </c>
       <c r="C41">
-        <v>22401100</v>
+        <v>2166048</v>
       </c>
       <c r="D41">
-        <v>22210616</v>
+        <v>1571950</v>
       </c>
       <c r="E41">
-        <v>22401100</v>
+        <v>2166048</v>
       </c>
       <c r="F41">
-        <v>1.00857625920866</v>
+        <v>1.3779369572823561</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C42">
-        <v>22401100</v>
+        <v>722016</v>
       </c>
       <c r="D42">
-        <v>22468932</v>
+        <v>553800</v>
       </c>
       <c r="E42">
-        <v>22401100</v>
+        <v>722016</v>
       </c>
       <c r="F42">
-        <v>0.99698107591406659</v>
+        <v>1.303748645720477</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
@@ -1428,22 +1428,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C43">
-        <v>22401100</v>
+        <v>948024</v>
       </c>
       <c r="D43">
-        <v>86011396</v>
+        <v>3674</v>
       </c>
       <c r="E43">
-        <v>22401100</v>
+        <v>948024</v>
       </c>
       <c r="F43">
-        <v>0.26044339519846882</v>
+        <v>258.03592814371262</v>
       </c>
       <c r="G43" t="b">
         <v>1</v>
@@ -1451,22 +1451,22 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C44">
-        <v>22401100</v>
+        <v>10000000</v>
       </c>
       <c r="D44">
-        <v>32584849</v>
+        <v>5543343</v>
       </c>
       <c r="E44">
-        <v>22401100</v>
+        <v>10000000</v>
       </c>
       <c r="F44">
-        <v>0.68746981150656861</v>
+        <v>1.803965585387735</v>
       </c>
       <c r="G44" t="b">
         <v>1</v>
@@ -1477,19 +1477,19 @@
         <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C45">
-        <v>22401100</v>
+        <v>2609729</v>
       </c>
       <c r="D45">
-        <v>27750084</v>
+        <v>968238</v>
       </c>
       <c r="E45">
-        <v>22401100</v>
+        <v>2609729</v>
       </c>
       <c r="F45">
-        <v>0.8072444032962206</v>
+        <v>2.6953383362355119</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C46">
-        <v>22401100</v>
+        <v>2874512</v>
       </c>
       <c r="D46">
-        <v>26573839</v>
+        <v>2291616</v>
       </c>
       <c r="E46">
-        <v>22401100</v>
+        <v>2874512</v>
       </c>
       <c r="F46">
-        <v>0.8429756799535062</v>
+        <v>1.2543602418555291</v>
       </c>
       <c r="G46" t="b">
         <v>1</v>
@@ -1520,22 +1520,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C47">
-        <v>2609729</v>
+        <v>2166048</v>
       </c>
       <c r="D47">
-        <v>1360134</v>
+        <v>2008371</v>
       </c>
       <c r="E47">
-        <v>2609729</v>
+        <v>2166048</v>
       </c>
       <c r="F47">
-        <v>1.9187293310806139</v>
+        <v>1.078509896826831</v>
       </c>
       <c r="G47" t="b">
         <v>1</v>
@@ -1543,22 +1543,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C48">
-        <v>2609729</v>
+        <v>722016</v>
       </c>
       <c r="D48">
-        <v>2614444</v>
+        <v>595992</v>
       </c>
       <c r="E48">
-        <v>2609729</v>
+        <v>722016</v>
       </c>
       <c r="F48">
-        <v>0.99819655727948275</v>
+        <v>1.2114525027181571</v>
       </c>
       <c r="G48" t="b">
         <v>1</v>
@@ -1566,22 +1566,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C49">
-        <v>2609729</v>
+        <v>948024</v>
       </c>
       <c r="D49">
-        <v>1861627</v>
+        <v>9207</v>
       </c>
       <c r="E49">
-        <v>2609729</v>
+        <v>948024</v>
       </c>
       <c r="F49">
-        <v>1.401853862239858</v>
+        <v>102.9677419354839</v>
       </c>
       <c r="G49" t="b">
         <v>1</v>
@@ -1589,22 +1589,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C50">
-        <v>2609729</v>
+        <v>10000000</v>
       </c>
       <c r="D50">
-        <v>926025</v>
+        <v>5309444</v>
       </c>
       <c r="E50">
-        <v>2609729</v>
+        <v>10000000</v>
       </c>
       <c r="F50">
-        <v>2.8182057719823979</v>
+        <v>1.883436382415937</v>
       </c>
       <c r="G50" t="b">
         <v>1</v>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B51" t="s">
         <v>9</v>
@@ -1621,13 +1621,13 @@
         <v>2609729</v>
       </c>
       <c r="D51">
-        <v>961811</v>
+        <v>908924</v>
       </c>
       <c r="E51">
         <v>2609729</v>
       </c>
       <c r="F51">
-        <v>2.713349088334402</v>
+        <v>2.8712290576549848</v>
       </c>
       <c r="G51" t="b">
         <v>1</v>
@@ -1635,22 +1635,22 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C52">
-        <v>2609729</v>
+        <v>2874512</v>
       </c>
       <c r="D52">
-        <v>1848300</v>
+        <v>2112903</v>
       </c>
       <c r="E52">
-        <v>2609729</v>
+        <v>2874512</v>
       </c>
       <c r="F52">
-        <v>1.411961802737651</v>
+        <v>1.3604562064609691</v>
       </c>
       <c r="G52" t="b">
         <v>1</v>
@@ -1658,22 +1658,22 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C53">
-        <v>2609729</v>
+        <v>2166048</v>
       </c>
       <c r="D53">
-        <v>1468424</v>
+        <v>1948227</v>
       </c>
       <c r="E53">
-        <v>2609729</v>
+        <v>2166048</v>
       </c>
       <c r="F53">
-        <v>1.7772312356649029</v>
+        <v>1.1118047332266721</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
@@ -1681,22 +1681,22 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B54" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C54">
-        <v>2609729</v>
+        <v>722016</v>
       </c>
       <c r="D54">
-        <v>968238</v>
+        <v>537389</v>
       </c>
       <c r="E54">
-        <v>2609729</v>
+        <v>722016</v>
       </c>
       <c r="F54">
-        <v>2.6953383362355119</v>
+        <v>1.34356304278651</v>
       </c>
       <c r="G54" t="b">
         <v>1</v>
@@ -1707,28 +1707,25 @@
         <v>21</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C55">
-        <v>2609729</v>
+        <v>948024</v>
       </c>
       <c r="D55">
-        <v>908924</v>
+        <v>7121</v>
       </c>
       <c r="E55">
-        <v>2609729</v>
+        <v>948024</v>
       </c>
       <c r="F55">
-        <v>2.8712290576549848</v>
+        <v>133.13074006459769</v>
       </c>
       <c r="G55" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G55">
-    <sortCondition ref="B1:B55"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>